--- a/artfynd/A 7475-2023 artfynd.xlsx
+++ b/artfynd/A 7475-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 7475-2023 artfynd.xlsx
+++ b/artfynd/A 7475-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,66 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>107663204</v>
+        <v>110680601</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ljungnäs 1:2, Sm</t>
+          <t>Ljungnäs, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584444.2445031708</v>
+        <v>584444</v>
       </c>
       <c r="R2" t="n">
-        <v>6321133.275086237</v>
+        <v>6321154</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -761,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-03-26</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-03-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,81 +764,63 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>107663129</v>
+        <v>110706783</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ljungnäs 1:2, Sm</t>
+          <t>Ljungnäs, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584476.2651946675</v>
+        <v>584444</v>
       </c>
       <c r="R3" t="n">
-        <v>6321221.575331716</v>
+        <v>6321154</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -890,22 +844,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-03-26</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-03-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2023-07-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Fanns på samma granlåga som ulltickan.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,78 +870,61 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>107660725</v>
+        <v>110644454</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ljungnäs 1:2, Sm</t>
+          <t>Ljungnäs, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584527.4173934145</v>
+        <v>584497</v>
       </c>
       <c r="R4" t="n">
-        <v>6321200.842480077</v>
+        <v>6321219</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1019,22 +951,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-03-26</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-03-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,78 +972,61 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>107662636</v>
+        <v>110680627</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ljungnäs 1:2, Sm</t>
+          <t>Ljungnäs, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584546.1127795066</v>
+        <v>584451</v>
       </c>
       <c r="R5" t="n">
-        <v>6321220.277505996</v>
+        <v>6321179</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1148,22 +1053,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-03-26</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-03-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2023-07-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1179,78 +1079,61 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>107662559</v>
+        <v>110680646</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ljungnäs 1:2, Sm</t>
+          <t>Ljungnäs, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584504.8211918683</v>
+        <v>584458</v>
       </c>
       <c r="R6" t="n">
-        <v>6321265.708438091</v>
+        <v>6321196</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1277,22 +1160,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-03-26</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-03-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1308,78 +1181,61 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>107662987</v>
+        <v>110680651</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ljungnäs 1:2, Sm</t>
+          <t>Ljungnäs, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584484.3312713885</v>
+        <v>584458</v>
       </c>
       <c r="R7" t="n">
-        <v>6321200.508448325</v>
+        <v>6321214</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1406,22 +1262,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-03-26</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-03-26</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1437,78 +1283,61 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>107660398</v>
+        <v>110680656</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ljungnäs 1:2, Sm</t>
+          <t>Ljungnäs, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584443.3403882325</v>
+        <v>584470</v>
       </c>
       <c r="R8" t="n">
-        <v>6321097.325994535</v>
+        <v>6321230</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1535,22 +1364,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-03-26</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-03-26</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1566,78 +1385,61 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>107662806</v>
+        <v>110680724</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ljungnäs 1:2, Sm</t>
+          <t>Ljungnäs, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584548.1854870548</v>
+        <v>584508</v>
       </c>
       <c r="R9" t="n">
-        <v>6321279.113607344</v>
+        <v>6321289</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1664,22 +1466,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-03-26</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-03-26</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1695,54 +1487,49 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>107661573</v>
+        <v>110898387</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1750,11 +1537,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1763,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584496.951442445</v>
+        <v>584458</v>
       </c>
       <c r="R10" t="n">
-        <v>6321223.630154074</v>
+        <v>6321168</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1793,22 +1576,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-03-26</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-03-26</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1836,42 +1609,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>107661484</v>
+        <v>112959917</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1879,11 +1647,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1892,10 +1656,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584562.7059673563</v>
+        <v>584529</v>
       </c>
       <c r="R11" t="n">
-        <v>6321262.533906057</v>
+        <v>6321165</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1922,22 +1686,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-03-26</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-03-26</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1965,55 +1719,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>107662605</v>
+        <v>110898437</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2021,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584588.2303640577</v>
+        <v>584492</v>
       </c>
       <c r="R12" t="n">
-        <v>6321214.60411358</v>
+        <v>6321161</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2051,22 +1795,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-03-26</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-03-26</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2094,66 +1828,52 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>107662665</v>
+        <v>110680803</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ljungnäs 1:2, Sm</t>
+          <t>Ljungnäs, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584564.5859487981</v>
+        <v>584521</v>
       </c>
       <c r="R13" t="n">
-        <v>6321250.595759439</v>
+        <v>6321164</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2180,22 +1900,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-03-26</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-03-26</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2211,78 +1921,69 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>107662097</v>
+        <v>110680696</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ljungnäs 1:2, Sm</t>
+          <t>Ljungnäs, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584677.5521146654</v>
+        <v>584522</v>
       </c>
       <c r="R14" t="n">
-        <v>6321248.002562658</v>
+        <v>6321256</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2309,22 +2010,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-03-26</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-03-26</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2333,85 +2024,75 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>107660843</v>
+        <v>110680785</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58238</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>103012</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ljungnäs 1:2, Sm</t>
+          <t>Ljungnäs, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584555.9272970514</v>
+        <v>584579</v>
       </c>
       <c r="R15" t="n">
-        <v>6321220.477709264</v>
+        <v>6321232</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2438,22 +2119,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-03-26</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-03-26</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2462,34 +2133,28 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>107661718</v>
+        <v>107660398</v>
       </c>
       <c r="B16" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2516,7 +2181,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2537,10 +2202,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584418.6814603918</v>
+        <v>584444</v>
       </c>
       <c r="R16" t="n">
-        <v>6321102.812185874</v>
+        <v>6321097</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2572,7 +2237,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2582,7 +2247,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2610,54 +2275,61 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>110644454</v>
+        <v>107660725</v>
       </c>
       <c r="B17" t="n">
-        <v>93388</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ljungnäs, Mörkeskog, Sm</t>
+          <t>Ljungnäs 1:2, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584497.0290945119</v>
+        <v>584527</v>
       </c>
       <c r="R17" t="n">
-        <v>6321219.821003045</v>
+        <v>6321201</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2684,22 +2356,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2023-03-26</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2023-03-26</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2715,27 +2387,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>110644866</v>
+        <v>107660843</v>
       </c>
       <c r="B18" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2762,10 +2429,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -2775,14 +2446,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ljungnäs, Mörkeskog, Sm</t>
+          <t>Ljungnäs 1:2, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584489.7487909471</v>
+        <v>584556</v>
       </c>
       <c r="R18" t="n">
-        <v>6321175.576707865</v>
+        <v>6321220</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2809,22 +2480,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2023-03-26</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2023-03-26</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2840,70 +2511,73 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>110680690</v>
+        <v>107661484</v>
       </c>
       <c r="B19" t="n">
-        <v>103288</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ljungnäs, Mörkeskog, Sm</t>
+          <t>Ljungnäs 1:2, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584521.9235214299</v>
+        <v>584562</v>
       </c>
       <c r="R19" t="n">
-        <v>6321256.258212781</v>
+        <v>6321262</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2930,22 +2604,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2023-03-26</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2023-03-26</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2961,66 +2635,73 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>110680724</v>
+        <v>107661573</v>
       </c>
       <c r="B20" t="n">
-        <v>93388</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ljungnäs, Mörkeskog, Sm</t>
+          <t>Ljungnäs 1:2, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584508.1719285614</v>
+        <v>584497</v>
       </c>
       <c r="R20" t="n">
-        <v>6321288.64085645</v>
+        <v>6321224</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -3047,22 +2728,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2023-03-26</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2023-03-26</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3078,66 +2759,73 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>110680656</v>
+        <v>107661718</v>
       </c>
       <c r="B21" t="n">
-        <v>93388</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ljungnäs, Mörkeskog, Sm</t>
+          <t>Ljungnäs 1:2, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584470.0900023666</v>
+        <v>584418</v>
       </c>
       <c r="R21" t="n">
-        <v>6321230.159719684</v>
+        <v>6321103</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3164,22 +2852,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2023-03-26</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2023-03-26</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3195,65 +2883,73 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>110680601</v>
+        <v>107662097</v>
       </c>
       <c r="B22" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ljungnäs, Mörkeskog, Sm</t>
+          <t>Ljungnäs 1:2, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584443.8232309618</v>
+        <v>584678</v>
       </c>
       <c r="R22" t="n">
-        <v>6321153.953720589</v>
+        <v>6321248</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3280,22 +2976,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2023-03-26</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2023-03-26</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3311,74 +3007,73 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>110680696</v>
+        <v>107662559</v>
       </c>
       <c r="B23" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ljungnäs, Mörkeskog, Sm</t>
+          <t>Ljungnäs 1:2, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584522</v>
+        <v>584504</v>
       </c>
       <c r="R23" t="n">
-        <v>6321256</v>
+        <v>6321266</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3405,12 +3100,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2023-03-26</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2023-03-26</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3419,75 +3124,80 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>110680803</v>
+        <v>107662605</v>
       </c>
       <c r="B24" t="n">
-        <v>89425</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ljungnäs, Mörkeskog, Sm</t>
+          <t>Ljungnäs 1:2, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584520.5272860702</v>
+        <v>584588</v>
       </c>
       <c r="R24" t="n">
-        <v>6321164.227454452</v>
+        <v>6321215</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3514,22 +3224,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2023-03-26</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2023-03-26</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3545,27 +3255,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>110680781</v>
+        <v>107662636</v>
       </c>
       <c r="B25" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3592,23 +3297,31 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ljungnäs, Mörkeskog, Sm</t>
+          <t>Ljungnäs 1:2, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584579.151008667</v>
+        <v>584546</v>
       </c>
       <c r="R25" t="n">
-        <v>6321231.839344994</v>
+        <v>6321220</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3635,22 +3348,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2023-03-26</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2023-03-26</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3666,70 +3379,73 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>110680708</v>
+        <v>107662665</v>
       </c>
       <c r="B26" t="n">
-        <v>103288</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ljungnäs, Mörkeskog, Sm</t>
+          <t>Ljungnäs 1:2, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584524.8162049708</v>
+        <v>584565</v>
       </c>
       <c r="R26" t="n">
-        <v>6321248.151399642</v>
+        <v>6321250</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3756,22 +3472,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2023-03-26</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2023-03-26</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3787,66 +3503,73 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>110680651</v>
+        <v>107662806</v>
       </c>
       <c r="B27" t="n">
-        <v>93388</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ljungnäs, Mörkeskog, Sm</t>
+          <t>Ljungnäs 1:2, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584458.4160649898</v>
+        <v>584549</v>
       </c>
       <c r="R27" t="n">
-        <v>6321214.134511985</v>
+        <v>6321279</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3873,22 +3596,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2023-03-26</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2023-03-26</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3904,66 +3627,73 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>110680627</v>
+        <v>107662862</v>
       </c>
       <c r="B28" t="n">
-        <v>93388</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ljungnäs, Mörkeskog, Sm</t>
+          <t>Ljungnäs 1:2, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584450.4016032883</v>
+        <v>584385</v>
       </c>
       <c r="R28" t="n">
-        <v>6321179.130026639</v>
+        <v>6321080</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3990,27 +3720,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2023-03-26</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2023-03-26</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4026,27 +3751,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>110680741</v>
+        <v>107662987</v>
       </c>
       <c r="B29" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4073,27 +3793,31 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ljungnäs, Mörkeskog, Sm</t>
+          <t>Ljungnäs 1:2, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584538.8927460162</v>
+        <v>584485</v>
       </c>
       <c r="R29" t="n">
-        <v>6321253.337963573</v>
+        <v>6321201</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -4120,22 +3844,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2023-03-26</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2023-03-26</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4151,70 +3875,73 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>110680674</v>
+        <v>107663129</v>
       </c>
       <c r="B30" t="n">
-        <v>103288</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ljungnäs, Mörkeskog, Sm</t>
+          <t>Ljungnäs 1:2, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584489.9203765931</v>
+        <v>584476</v>
       </c>
       <c r="R30" t="n">
-        <v>6321247.439931343</v>
+        <v>6321221</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4241,22 +3968,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2023-03-26</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2023-03-26</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4272,74 +3999,73 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>110680785</v>
+        <v>107663204</v>
       </c>
       <c r="B31" t="n">
-        <v>56635</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103012</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ljungnäs, Mörkeskog, Sm</t>
+          <t>Ljungnäs 1:2, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584579.151008667</v>
+        <v>584444</v>
       </c>
       <c r="R31" t="n">
-        <v>6321231.839344994</v>
+        <v>6321133</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4366,22 +4092,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-26</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4390,60 +4106,64 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>110680646</v>
+        <v>110644866</v>
       </c>
       <c r="B32" t="n">
-        <v>93388</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
@@ -4452,10 +4172,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584458.2367180064</v>
+        <v>584489</v>
       </c>
       <c r="R32" t="n">
-        <v>6321196.165905406</v>
+        <v>6321176</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4485,19 +4205,9 @@
           <t>2023-07-06</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-07-06</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4525,15 +4235,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>110706783</v>
+        <v>110680741</v>
       </c>
       <c r="B33" t="n">
-        <v>89845</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4541,26 +4246,35 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4568,13 +4282,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584443.8232309618</v>
+        <v>584539</v>
       </c>
       <c r="R33" t="n">
-        <v>6321153.953720589</v>
+        <v>6321253</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4601,24 +4315,9 @@
           <t>2023-07-06</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-07-06</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Fanns på samma granlåga som ulltickan.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4646,15 +4345,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>110898187</v>
+        <v>110680781</v>
       </c>
       <c r="B34" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4681,31 +4375,23 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Ljungnäs 1:2, Sm</t>
+          <t>Ljungnäs, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584579.8850266705</v>
+        <v>584579</v>
       </c>
       <c r="R34" t="n">
-        <v>6321222.59968644</v>
+        <v>6321232</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4735,19 +4421,9 @@
           <t>2023-07-06</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2023-07-06</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4763,27 +4439,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>110899102</v>
+        <v>110898187</v>
       </c>
       <c r="B35" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4810,7 +4481,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4831,10 +4502,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>584537.266680731</v>
+        <v>584580</v>
       </c>
       <c r="R35" t="n">
-        <v>6321226.085374341</v>
+        <v>6321223</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4864,19 +4535,9 @@
           <t>2023-07-06</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2023-07-06</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4904,50 +4565,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>110898437</v>
+        <v>110898250</v>
       </c>
       <c r="B36" t="n">
-        <v>89802</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4955,10 +4616,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>584491.6840554716</v>
+        <v>584564</v>
       </c>
       <c r="R36" t="n">
-        <v>6321160.917422781</v>
+        <v>6321222</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4988,19 +4649,9 @@
           <t>2023-07-06</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-07-06</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5028,42 +4679,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>110898387</v>
+        <v>110898336</v>
       </c>
       <c r="B37" t="n">
-        <v>93388</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5071,7 +4717,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
@@ -5080,10 +4730,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584457.7116934793</v>
+        <v>584473</v>
       </c>
       <c r="R37" t="n">
-        <v>6321168.391038232</v>
+        <v>6321225</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -5113,19 +4763,9 @@
           <t>2023-07-06</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2023-07-06</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5153,15 +4793,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>110898336</v>
+        <v>110899102</v>
       </c>
       <c r="B38" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5188,7 +4823,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5209,10 +4844,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584472.9382402588</v>
+        <v>584537</v>
       </c>
       <c r="R38" t="n">
-        <v>6321224.229478865</v>
+        <v>6321226</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -5242,19 +4877,9 @@
           <t>2023-07-06</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2023-07-06</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5282,15 +4907,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>110898250</v>
+        <v>112959887</v>
       </c>
       <c r="B39" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5317,7 +4937,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5338,10 +4958,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>584564.072755578</v>
+        <v>584517</v>
       </c>
       <c r="R39" t="n">
-        <v>6321222.277056703</v>
+        <v>6321159</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5368,22 +4988,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5414,12 +5024,7 @@
         <v>112959892</v>
       </c>
       <c r="B40" t="n">
-        <v>97298</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5470,7 +5075,7 @@
         <v>584478</v>
       </c>
       <c r="R40" t="n">
-        <v>6321142</v>
+        <v>6321141</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5533,12 +5138,7 @@
         <v>112959898</v>
       </c>
       <c r="B41" t="n">
-        <v>97298</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5652,12 +5252,7 @@
         <v>112959982</v>
       </c>
       <c r="B42" t="n">
-        <v>97298</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5708,7 +5303,7 @@
         <v>584494</v>
       </c>
       <c r="R42" t="n">
-        <v>6321258</v>
+        <v>6321259</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5768,66 +5363,53 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>112959887</v>
+        <v>110680674</v>
       </c>
       <c r="B43" t="n">
-        <v>97298</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Ljungnäs 1:2, Sm</t>
+          <t>Ljungnäs, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584517</v>
+        <v>584490</v>
       </c>
       <c r="R43" t="n">
-        <v>6321159</v>
+        <v>6321248</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5854,12 +5436,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2023-10-27</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2023-10-27</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5875,15 +5457,227 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>110680690</v>
+      </c>
+      <c r="B44" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Ljungnäs, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>584522</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6321256</v>
+      </c>
+      <c r="S44" t="n">
+        <v>25</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2023-07-06</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2023-07-06</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>110680708</v>
+      </c>
+      <c r="B45" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Ljungnäs, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>584525</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6321248</v>
+      </c>
+      <c r="S45" t="n">
+        <v>25</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2023-07-06</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2023-07-06</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7475-2023 artfynd.xlsx
+++ b/artfynd/A 7475-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AZ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110680601</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110706783</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110644454</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110680627</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1190,6 +1215,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110680646</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1292,6 +1322,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110680651</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1394,6 +1429,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110680656</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1496,6 +1536,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110680724</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1606,6 +1651,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110898387</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1716,6 +1766,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112959917</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1825,6 +1880,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110898437</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1930,6 +1990,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110680803</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2039,6 +2104,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110680696</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2148,6 +2218,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110680785</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2272,6 +2347,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107660398</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2396,6 +2476,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107660725</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2520,6 +2605,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107660843</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2644,6 +2734,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107661484</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2768,6 +2863,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107661573</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2892,6 +2992,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107661718</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3016,6 +3121,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107662097</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3140,6 +3250,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107662559</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3264,6 +3379,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107662605</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3388,6 +3508,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107662636</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3512,6 +3637,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107662665</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3636,6 +3766,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107662806</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3760,6 +3895,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107662862</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3884,6 +4024,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107662987</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4008,6 +4153,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107663129</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4122,6 +4272,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107663204</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4232,6 +4387,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110644866</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4342,6 +4502,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110680741</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4448,6 +4613,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110680781</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4562,6 +4732,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110898187</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4676,6 +4851,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110898250</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4790,6 +4970,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110898336</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4904,6 +5089,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110899102</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5018,6 +5208,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112959887</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5132,6 +5327,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112959892</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5246,6 +5446,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112959898</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5360,6 +5565,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112959982</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5466,6 +5676,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110680674</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5572,6 +5787,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110680690</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5678,8 +5898,59 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110680708</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>